--- a/artfynd/A 39165-2024 artfynd.xlsx
+++ b/artfynd/A 39165-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,57 +675,73 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>81409679</v>
+        <v>128830113</v>
       </c>
       <c r="B2" t="n">
-        <v>100515</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>12921</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>223246</v>
+        <v>100405</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skogsalm</t>
+          <t>Getingrovfluga</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Ulmus glabra</t>
+          <t>Asilus crabroniformis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Huds.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>vilande</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Brödåkraskogen, 300 m SV om SOLHEM, Sk</t>
+          <t>Getingrovfluga Brödåkra, Sk</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>376239.6979551855</v>
+        <v>376103</v>
       </c>
       <c r="R2" t="n">
-        <v>6200674.242799841</v>
+        <v>6200619</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -749,22 +765,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2014-05-26</t>
+          <t>2025-09-25</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2014-05-26</t>
+          <t>2025-09-25</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,39 +793,25 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Lövskog/åkerkant</t>
-        </is>
-      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Stefan Andersson</t>
+          <t>Karl-Erik Söderqvist</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Roland Lyhagen</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>Skånes Flora Millora 2008-2015</t>
-        </is>
-      </c>
+          <t>Karl-Erik Söderqvist</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
         <v>81409799</v>
       </c>
       <c r="B3" t="n">
-        <v>103813</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -841,10 +843,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>376239.6979551855</v>
+        <v>376240</v>
       </c>
       <c r="R3" t="n">
-        <v>6200674.242799841</v>
+        <v>6200674</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -874,19 +876,9 @@
           <t>2014-05-26</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2014-05-26</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -920,6 +912,117 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr">
+        <is>
+          <t>Skånes Flora Millora 2008-2015</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>81409679</v>
+      </c>
+      <c r="B4" t="n">
+        <v>103403</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>223246</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Skogsalm</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Ulmus glabra</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Huds.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Brödåkraskogen, 300 m SV om SOLHEM, Sk</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>376240</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6200674</v>
+      </c>
+      <c r="S4" t="n">
+        <v>50</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Svalöv</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Sireköpinge</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2014-05-26</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2014-05-26</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Lövskog/åkerkant</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Stefan Andersson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Roland Lyhagen</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
         <is>
           <t>Skånes Flora Millora 2008-2015</t>
         </is>

--- a/artfynd/A 39165-2024 artfynd.xlsx
+++ b/artfynd/A 39165-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -805,6 +810,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128830113</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -914,6 +924,11 @@
       <c r="AY3" t="inlineStr">
         <is>
           <t>Skånes Flora Millora 2008-2015</t>
+        </is>
+      </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81409799</t>
         </is>
       </c>
     </row>
@@ -1027,8 +1042,18 @@
           <t>Skånes Flora Millora 2008-2015</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81409679</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>